--- a/Evidence/PP/COCOMO I and II Calculations/COCOMO I & II Calculations Sprint 2.xlsx
+++ b/Evidence/PP/COCOMO I and II Calculations/COCOMO I & II Calculations Sprint 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neelp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373FBACC-4494-413C-A946-3BDB211643E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB38BAF-694B-4E7F-A539-1836DA12A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8C05499B-E777-4CB1-ACAA-0667EC699DC3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="73">
   <si>
     <t>COCOMO I</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>File name</t>
-  </si>
-  <si>
-    <t>__init__</t>
   </si>
   <si>
     <t>LOC</t>
@@ -310,6 +307,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5BB3535-9357-4C74-9BEA-22189AB591AE}" name="Table1" displayName="Table1" ref="A22:F35" totalsRowShown="0">
+  <autoFilter ref="A22:F35" xr:uid="{D5BB3535-9357-4C74-9BEA-22189AB591AE}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{32891DE5-E573-4AD0-9F52-99409EEB65E0}" name="File name"/>
+    <tableColumn id="2" xr3:uid="{5A208F0D-91E6-4030-BBE1-310A3FFFF8E7}" name="LOC"/>
+    <tableColumn id="3" xr3:uid="{63F3DAFF-AD6D-484D-8AF6-797B6E7B6552}" name="KLOC"/>
+    <tableColumn id="4" xr3:uid="{A20994D7-D210-475B-AC18-30F9328725F0}" name="E (Without EAF)"/>
+    <tableColumn id="5" xr3:uid="{98DD15A6-CC61-4581-9438-30867B1A82A1}" name="D (Without EAF)"/>
+    <tableColumn id="6" xr3:uid="{4843797B-C021-4028-9DE9-F908D4E6A6B1}" name="P (Without EAF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,15 +641,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEAEC6C2-1035-40B4-B580-094FC01FC123}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.26953125" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -647,7 +659,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
         <v>6</v>
@@ -667,7 +679,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3">
         <v>2.4</v>
@@ -684,183 +696,183 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>1.1499999999999999</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>1.1499999999999999</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17">
         <v>0.95</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18">
         <v>0.91</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19">
         <v>1.1000000000000001</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20">
         <f>PRODUCT(B5:B19)</f>
@@ -872,29 +884,24 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
         <v>1</v>
       </c>
       <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24">
         <v>150</v>
@@ -918,7 +925,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25">
         <v>75</v>
@@ -942,7 +949,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -966,7 +973,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27">
         <v>280</v>
@@ -990,7 +997,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B28">
         <v>300</v>
@@ -1014,7 +1021,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29">
         <v>175</v>
@@ -1038,7 +1045,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -1062,7 +1069,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>50</v>
@@ -1084,217 +1091,220 @@
         <v>9.7908508334670977E-2</v>
       </c>
     </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34">
+        <f>SUM(B24:B31)</f>
+        <v>1230</v>
+      </c>
+      <c r="C34">
+        <f>B34/1000</f>
+        <v>1.23</v>
+      </c>
+      <c r="D34">
+        <f>2.4*C34^1.05</f>
+        <v>2.982713972873857</v>
+      </c>
+      <c r="E34">
+        <f>2.5*D34^0.38</f>
+        <v>3.7869748420326692</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ref="F34" si="4">D34/E34</f>
+        <v>0.78762444887879879</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35">
+        <f>B34</f>
+        <v>1230</v>
+      </c>
+      <c r="C35">
+        <f>B35/1000</f>
+        <v>1.23</v>
+      </c>
+      <c r="D35">
+        <f>2.4*(C35^1.05)*B20</f>
+        <v>3.7511546749370619</v>
+      </c>
+      <c r="E35">
+        <f>2.5*(D35^0.38)</f>
+        <v>4.1316421382672095</v>
+      </c>
+      <c r="F35">
+        <f t="shared" ref="F35" si="5">D35/E35</f>
+        <v>0.90790890144960079</v>
+      </c>
+    </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39">
-        <f>SUM(B24:B36)</f>
-        <v>1230</v>
-      </c>
-      <c r="C39">
-        <f>B39/1000</f>
-        <v>1.23</v>
-      </c>
-      <c r="D39">
-        <f>2.4*C39^1.05</f>
-        <v>2.982713972873857</v>
-      </c>
-      <c r="E39">
-        <f>2.5*D39^0.38</f>
-        <v>3.7869748420326692</v>
-      </c>
-      <c r="F39">
-        <f t="shared" ref="F39" si="4">D39/E39</f>
-        <v>0.78762444887879879</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40">
-        <f>B39</f>
-        <v>1230</v>
-      </c>
-      <c r="C40">
-        <f>B40/1000</f>
-        <v>1.23</v>
-      </c>
-      <c r="D40">
-        <f>2.4*(C40^1.05)*B20</f>
-        <v>3.7511546749370619</v>
-      </c>
-      <c r="E40">
-        <f>2.5*(D40^0.38)</f>
-        <v>4.1316421382672095</v>
-      </c>
-      <c r="F40">
-        <f t="shared" ref="F40" si="5">D40/E40</f>
-        <v>0.90790890144960079</v>
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <v>3.72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <v>3.04</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
+        <v>4.24</v>
+      </c>
+      <c r="C43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>2.19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>6.24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46">
+        <f>SUM(B41:B45)</f>
+        <v>19.43</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B48">
-        <v>3.72</v>
-      </c>
-      <c r="C48" t="s">
-        <v>50</v>
+        <f>C34</f>
+        <v>1.23</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B49">
-        <v>3.04</v>
-      </c>
-      <c r="C49" t="s">
-        <v>31</v>
+        <f>B46</f>
+        <v>19.43</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B50">
-        <v>4.24</v>
-      </c>
-      <c r="C50" t="s">
-        <v>50</v>
+        <f>B20</f>
+        <v>1.2576313750000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>2.19</v>
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <v>6.24</v>
-      </c>
-      <c r="C52" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53">
-        <f>SUM(B48:B52)</f>
-        <v>19.43</v>
+        <f>2.4*B50*(B48)^(1.05+(0.01*B49))</f>
+        <v>3.9051123708151541</v>
+      </c>
+      <c r="C53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <f>2.5*(B53)^0.38</f>
+        <v>4.1952780721922656</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B55">
-        <f>C39</f>
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56">
-        <f>B53</f>
-        <v>19.43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57">
-        <f>B20</f>
-        <v>1.2576313750000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60">
-        <f>2.4*B57*(B55)^(1.05+(0.01*B56))</f>
-        <v>3.9051123708151541</v>
-      </c>
-      <c r="C60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B61">
-        <f>2.5*(B60)^0.38</f>
-        <v>4.1952780721922656</v>
-      </c>
-      <c r="C61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+        <f xml:space="preserve"> B53/B54</f>
+        <v>0.93083516840029534</v>
+      </c>
+      <c r="C55" t="s">
         <v>64</v>
-      </c>
-      <c r="B62">
-        <f xml:space="preserve"> B60/B61</f>
-        <v>0.93083516840029534</v>
-      </c>
-      <c r="C62" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>